--- a/BrotherCafe/src/com/cafe/connect/thongke.xlsx
+++ b/BrotherCafe/src/com/cafe/connect/thongke.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="55">
   <si>
     <t/>
   </si>
@@ -82,7 +82,7 @@
     <t>Cafe Muối</t>
   </si>
   <si>
-    <t>2023-10-15</t>
+    <t>2023-12-12</t>
   </si>
   <si>
     <t>Cafe Sữa</t>
@@ -103,34 +103,16 @@
     <t>phatdv</t>
   </si>
   <si>
-    <t>Chưa Thanh Toán</t>
-  </si>
-  <si>
-    <t>B03</t>
-  </si>
-  <si>
-    <t>19:05:33.0000000</t>
-  </si>
-  <si>
-    <t>21:55:55.0000000</t>
-  </si>
-  <si>
-    <t>kietlt</t>
-  </si>
-  <si>
     <t>Đã Thanh Toán</t>
   </si>
   <si>
     <t>B06</t>
   </si>
   <si>
-    <t>2023-10-14 19:10:01.0</t>
-  </si>
-  <si>
     <t>18:20:33.0000000</t>
   </si>
   <si>
-    <t>20:29:17.0000000</t>
+    <t>15:04:20.0000000</t>
   </si>
   <si>
     <t>vinhvtt</t>
@@ -412,7 +394,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="B4" t="s">
         <v>30</v>
@@ -433,10 +415,10 @@
         <v>33</v>
       </c>
       <c r="H4" t="n">
-        <v>20002.0</v>
+        <v>50000.0</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -444,28 +426,28 @@
         <v>6.0</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H5" t="n">
-        <v>30001.0</v>
+        <v>50000.0</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -502,22 +484,22 @@
         <v>5.0</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H7" t="n">
         <v>32000.0</v>
@@ -531,22 +513,22 @@
         <v>5.0</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H8" t="n">
         <v>32000.0</v>
@@ -587,76 +569,76 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
         <v>46</v>
       </c>
-      <c r="D4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" t="s">
-        <v>52</v>
-      </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s">
         <v>46</v>
       </c>
-      <c r="D5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" t="s">
-        <v>52</v>
-      </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>25</v>
@@ -667,22 +649,22 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
